--- a/data/workbooks/test1-marking.xlsx
+++ b/data/workbooks/test1-marking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude\DoktoraTez\AI-Tests\github\data\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C59A721-371C-43C4-A690-C32912D048DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF9288E-1743-4958-945A-CEA2BF62DED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5490" yWindow="1755" windowWidth="21600" windowHeight="12555" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="565">
   <si>
     <t>ady-kbd AI Language Testing Tool</t>
   </si>
@@ -1965,16 +1965,19 @@
     <t>yanlış ve anlamsız / непонятно</t>
   </si>
   <si>
-    <t>Çeviri cümlesi çevrilen cümleyi karşılamıyor.</t>
-  </si>
-  <si>
-    <t>Çeviri cümlesi çevrilen cümleyi kısmen karşılamış.</t>
-  </si>
-  <si>
-    <t>зэ fazladan yazılmış.</t>
-  </si>
-  <si>
     <t>(доум кунэм) ifadesi türkçe doğum günü ifadesini çağrıştırıyor fakat GT ile dil algıla ile bakınca Tacikçe "доум кунем" olarak "dua edelim." şeklinde çevrildi.</t>
+  </si>
+  <si>
+    <t>Gerçek farkı buldu, ama olmayan farklar da üretti.</t>
+  </si>
+  <si>
+    <t>Yazı sistemi karışıklığı.</t>
+  </si>
+  <si>
+    <t>Yalnız olmayan farklar üretti.</t>
+  </si>
+  <si>
+    <t>Fark yok dedi.</t>
   </si>
 </sst>
 </file>
@@ -3352,7 +3355,11 @@
         <v>550</v>
       </c>
       <c r="L5" s="3"/>
-      <c r="M5" s="5"/>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Hedef dilde yanıt yok: İngilizce açıklama (Adıgece selamı çözümledi).</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="71.25" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -4353,7 +4360,9 @@
       <c r="L32" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="M32" s="5"/>
+      <c r="M32" s="5" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="33" spans="1:13" ht="213.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
@@ -4392,7 +4401,9 @@
       <c r="L33" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="M33" s="5"/>
+      <c r="M33" s="5" t="s">
+        <v>561</v>
+      </c>
     </row>
     <row r="34" spans="1:13" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
@@ -4431,7 +4442,9 @@
       <c r="L34" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="M34" s="5"/>
+      <c r="M34" s="5" t="s">
+        <v>561</v>
+      </c>
     </row>
     <row r="35" spans="1:13" ht="299.25" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
@@ -4470,7 +4483,9 @@
       <c r="L35" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="M35" s="5"/>
+      <c r="M35" s="5" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="36" spans="1:13" ht="128.25" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
@@ -4509,7 +4524,9 @@
       <c r="L36" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="M36" s="5"/>
+      <c r="M36" s="5" t="s">
+        <v>561</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
@@ -4846,8 +4863,10 @@
       <c r="D7" s="3">
         <v>2</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>312</v>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сэ Клод сыкъэуцущт — Anthropic-м къыгъэхьазырыгъэ AI-компьютерым сикӏэсэшху (искусственнэ интеллект).</t>
+        </is>
       </c>
       <c r="F7" s="3">
         <v>9</v>
@@ -4890,8 +4909,10 @@
       <c r="D8" s="3">
         <v>3</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>313</v>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сэ шъуиупчӏэхэм джэуап сэты, тхылъхэм садэлажьэ, тхэным садэӏэпыӏэн, тхьапэхэр сэшӏы, интернетым сэлъыхъу ищыкӏагъэмэ, нэмыкӏ куп Iофыгъохэми сыдэлажьэ.</t>
+        </is>
       </c>
       <c r="F8" s="3">
         <v>17</v>
@@ -4917,7 +4938,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T8" s="5"/>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="1:20" ht="57" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -4932,8 +4957,10 @@
       <c r="D9" s="3">
         <v>4</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>314</v>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Шъукъызэрэдэсэшъоу зэхэсэтэу — адыгабзэм зэрэсэшӏэрэр икӏу зэрэс, ащ фэшI гухэкӏышхоу шъоджэуап пштынэу симыфаемэ, урысыбзэкӏэ е инджылызыбзэкӏэ дэгъоу тыгущыIэн тлъэкIыщт.</t>
+        </is>
       </c>
       <c r="F9" s="3">
         <v>18</v>
@@ -4963,7 +4990,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T9" s="5"/>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -4978,8 +5009,10 @@
       <c r="D10" s="3">
         <v>5</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>315</v>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сыда шъуикIалэсэп — тыгущыIэн тфай сыда?</t>
+        </is>
       </c>
       <c r="F10" s="3">
         <v>5</v>
@@ -5009,7 +5042,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T10" s="5"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
@@ -6564,8 +6601,10 @@
       <c r="D48" s="3">
         <v>2</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>351</v>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сэ гущыӏэхэр зэхэслъхьэ, ау ар цӏыфым фэдэу "гупшысэн" ара, хьаумэ гущыӏэ шапхъэхэм ателъытагъэу джэуап къэсэты ара — ащ пае шъыпкъэ джэуап зимыӏэ Iофыгъу горэм фэдэу щыт.</t>
+        </is>
       </c>
       <c r="F48" s="3">
         <v>25</v>
@@ -6595,7 +6634,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T48" s="5"/>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="49" spans="1:20" ht="71.25" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
@@ -6610,8 +6653,10 @@
       <c r="D49" s="3">
         <v>3</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>352</v>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нахь шъыпкъэу къэпIон хъумэ: сэ шIэныгъэ шхьэхынэу зыми фэдэ гупшысэ соригинальнэ сиIэп зэрэ жъугъэIуагъэпэрапцIэу, ау зыдэсэлажьэрэ упчIэм иджэуап согъэхьазыры зэрэ-алгоритмым (математикэ шапхъэхэм) атетэу.</t>
+        </is>
       </c>
       <c r="F49" s="3">
         <v>23</v>
@@ -6645,7 +6690,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="T49" s="5"/>
+      <c r="T49" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
@@ -7110,8 +7159,10 @@
       <c r="D60" s="3">
         <v>1</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>363</v>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ары, сэ зэдзэкӏыныр сшIэшъущт!</t>
+        </is>
       </c>
       <c r="F60" s="3">
         <v>4</v>
@@ -7139,7 +7190,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T60" s="5"/>
+      <c r="T60" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="61" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
@@ -7154,8 +7209,10 @@
       <c r="D61" s="3">
         <v>2</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>364</v>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тхыгъэр е гущыIэр къысэты, сэ сшIошI (адыгабзэ, урысыбзэ, инджылызыбзэ, нэмыкI бзэхэри) — зэрэшъуфэягъэм тетэу зэсдзэкIыщт.</t>
+        </is>
       </c>
       <c r="F61" s="3">
         <v>14</v>
@@ -7185,7 +7242,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T61" s="5"/>
+      <c r="T61" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="62" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
@@ -7675,9 +7736,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T72" s="5" t="s">
-        <v>560</v>
-      </c>
+      <c r="T72" s="5"/>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
@@ -7805,9 +7864,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T75" s="5" t="s">
-        <v>560</v>
-      </c>
+      <c r="T75" s="5"/>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
@@ -7893,9 +7950,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T77" s="5" t="s">
-        <v>560</v>
-      </c>
+      <c r="T77" s="5"/>
     </row>
     <row r="78" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
@@ -7939,9 +7994,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T78" s="5" t="s">
-        <v>560</v>
-      </c>
+      <c r="T78" s="5"/>
     </row>
     <row r="79" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
@@ -7985,7 +8038,7 @@
       </c>
       <c r="T79" s="5"/>
     </row>
-    <row r="80" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>245</v>
       </c>
@@ -8027,9 +8080,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T80" s="5" t="s">
-        <v>561</v>
-      </c>
+      <c r="T80" s="5"/>
     </row>
     <row r="81" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
@@ -8632,8 +8683,10 @@
       <c r="D95" s="3">
         <v>14</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>397</v>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зыгорэм ебгъэзэжьынэу фаемэ е нэмыкI гущыIэ шIыкIэ пщэлъэгъун фаеу хъумэ къысаIо.</t>
+        </is>
       </c>
       <c r="F95" s="3">
         <v>11</v>
@@ -8661,7 +8714,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T95" s="5"/>
+      <c r="T95" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="96" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
@@ -9255,7 +9312,7 @@
       </c>
       <c r="T109" s="5"/>
     </row>
-    <row r="110" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>253</v>
       </c>
@@ -9297,9 +9354,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T110" s="5" t="s">
-        <v>561</v>
-      </c>
+      <c r="T110" s="5"/>
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
@@ -9385,7 +9440,7 @@
       </c>
       <c r="T112" s="5"/>
     </row>
-    <row r="113" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>253</v>
       </c>
@@ -9427,9 +9482,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T113" s="5" t="s">
-        <v>561</v>
-      </c>
+      <c r="T113" s="5"/>
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
@@ -9515,7 +9568,7 @@
       </c>
       <c r="T115" s="5"/>
     </row>
-    <row r="116" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>253</v>
       </c>
@@ -9537,10 +9590,10 @@
       <c r="G116" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="H116" s="4"/>
-      <c r="I116" s="4">
-        <v>1</v>
-      </c>
+      <c r="H116" s="4">
+        <v>1</v>
+      </c>
+      <c r="I116" s="4"/>
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="3">
@@ -9557,9 +9610,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T116" s="5" t="s">
-        <v>561</v>
-      </c>
+      <c r="T116" s="5"/>
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
@@ -9687,7 +9738,7 @@
       </c>
       <c r="T119" s="5"/>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>255</v>
       </c>
@@ -9707,15 +9758,17 @@
         <v>2</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="H120" s="4"/>
+        <v>558</v>
+      </c>
+      <c r="H120" s="4">
+        <v>1</v>
+      </c>
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
       <c r="L120" s="3">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
@@ -10107,7 +10160,7 @@
       </c>
       <c r="T129" s="5"/>
     </row>
-    <row r="130" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>255</v>
       </c>
@@ -10129,15 +10182,17 @@
       <c r="G130" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="H130" s="4"/>
+      <c r="H130" s="4">
+        <v>2</v>
+      </c>
       <c r="I130" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
       <c r="L130" s="3">
         <f t="shared" ref="L130:L193" si="4">F130-(H130+I130+J130+K130)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M130" s="4"/>
       <c r="N130" s="4"/>
@@ -10149,9 +10204,7 @@
         <f t="shared" ref="S130:S193" si="5">N130+O130+P130+Q130+R130</f>
         <v>0</v>
       </c>
-      <c r="T130" s="5" t="s">
-        <v>561</v>
-      </c>
+      <c r="T130" s="5"/>
     </row>
     <row r="131" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
@@ -10679,9 +10732,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T142" s="5" t="s">
-        <v>562</v>
-      </c>
+      <c r="T142" s="5"/>
     </row>
     <row r="143" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
@@ -11302,8 +11353,10 @@
       <c r="D157" s="3">
         <v>13</v>
       </c>
-      <c r="E157" s="2" t="s">
-        <v>448</v>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тхьам унэгъо пытэ, унэгъо бай ашIынхэу, амал дэгъухэри насып дэгъухэри къаритынэу сафэлъаӏо.»</t>
+        </is>
       </c>
       <c r="F157" s="3">
         <v>12</v>
@@ -11331,7 +11384,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T157" s="5"/>
+      <c r="T157" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="158" spans="1:20" ht="57" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
@@ -11346,8 +11403,10 @@
       <c r="D158" s="3">
         <v>14</v>
       </c>
-      <c r="E158" s="2" t="s">
-        <v>449</v>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зэшым иныбджэгъу "ыныбжь мафэ" (doğum günü) зыфэхъурэ пычыгъор дегъэзыжьыгъэ — блэкӏыгъэ джэуапым "нысащэ" арыгъэшти, ащ фэдэу зэсдзэкӏыгъэ шIыкIэр зэблэсхъугъ.</t>
+        </is>
       </c>
       <c r="F158" s="3">
         <v>18</v>
@@ -11379,7 +11438,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T158" s="5"/>
+      <c r="T158" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
@@ -12363,7 +12426,7 @@
       </c>
       <c r="T181" s="5"/>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>267</v>
       </c>
@@ -12383,15 +12446,17 @@
         <v>2</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="H182" s="4"/>
+        <v>558</v>
+      </c>
+      <c r="H182" s="4">
+        <v>1</v>
+      </c>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
       <c r="L182" s="3">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M182" s="4"/>
       <c r="N182" s="4"/>
@@ -13022,8 +13087,10 @@
       <c r="D197" s="3">
         <v>2</v>
       </c>
-      <c r="E197" s="2" t="s">
-        <v>469</v>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пчыхьэ дах, унагъо зэрэугъоигъэ, зэшым инысащэ хъугъэ шIыкIэ, ежьхэри зэрэшIу зэдэштэрэр къыхэлъытэгъэ Iоф ары зэдзэкIыгъэ параграфитIумкIи къэIуагъэр.</t>
+        </is>
       </c>
       <c r="F197" s="3">
         <v>17</v>
@@ -13055,7 +13122,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T197" s="5"/>
+      <c r="T197" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="198" spans="1:20" ht="57" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
@@ -13070,8 +13141,10 @@
       <c r="D198" s="3">
         <v>3</v>
       </c>
-      <c r="E198" s="2" t="s">
-        <v>470</v>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ау зы Iахь зэтемыфагъэ щыI: апэрэ параграфым зэшым иныбджэгъу инысащэ (свадьба) нэIуасэ зыфэхъугъагъэу ыIуагъ, ятIонэрэм ащ ыныбжь мафэм (день рождения) ары зыфэхъугъагъэр ыIуагъ.</t>
+        </is>
       </c>
       <c r="F198" s="3">
         <v>23</v>
@@ -13101,7 +13174,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T198" s="5"/>
+      <c r="T198" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="199" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
@@ -13393,25 +13470,27 @@
       <c r="G205" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="H205" s="4">
-        <v>1</v>
-      </c>
+      <c r="H205" s="4"/>
       <c r="I205" s="4"/>
       <c r="J205" s="4"/>
-      <c r="K205" s="4"/>
+      <c r="K205" s="4">
+        <v>1</v>
+      </c>
       <c r="L205" s="3">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M205" s="4"/>
-      <c r="N205" s="4"/>
+      <c r="N205" s="4">
+        <v>1</v>
+      </c>
       <c r="O205" s="4"/>
       <c r="P205" s="4"/>
       <c r="Q205" s="4"/>
       <c r="R205" s="4"/>
       <c r="S205" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T205" s="5"/>
     </row>
@@ -13604,8 +13683,10 @@
       <c r="D210" s="3">
         <v>2</v>
       </c>
-      <c r="E210" s="2" t="s">
-        <v>482</v>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нахь инэу зэфэшъхьафыр: апэрэ параграфым зэшым иныбджэгъу инысащэм (свадьбэм) нысэр нэIуасэ зыфищыгъагъэу ыIуагъ, ятIонэрэ параграфым ащ ыныбжь мафэм (день рождения) нэIуасэ зыфэхъугъагъэу ыIуагъ.</t>
+        </is>
       </c>
       <c r="F210" s="3">
         <v>23</v>
@@ -13635,7 +13716,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T210" s="5"/>
+      <c r="T210" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="211" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
@@ -13650,8 +13735,10 @@
       <c r="D211" s="3">
         <v>3</v>
       </c>
-      <c r="E211" s="2" t="s">
-        <v>483</v>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ар зы шIыкIэ ары — тарихъыр зэфэшъхьаф.</t>
+        </is>
       </c>
       <c r="F211" s="3">
         <v>6</v>
@@ -13679,7 +13766,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T211" s="5"/>
+      <c r="T211" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="212" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
@@ -13694,8 +13785,10 @@
       <c r="D212" s="3">
         <v>4</v>
       </c>
-      <c r="E212" s="2" t="s">
-        <v>484</v>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">НахьыкIэу зэфэшъхьафхэр:</t>
+        </is>
       </c>
       <c r="F212" s="3">
         <v>2</v>
@@ -13723,7 +13816,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T212" s="5"/>
+      <c r="T212" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="213" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
@@ -13738,8 +13835,10 @@
       <c r="D213" s="3">
         <v>5</v>
       </c>
-      <c r="E213" s="2" t="s">
-        <v>485</v>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Апэрэм "унэгъо ӏужъ" (тэрэзэу — "долговечная семья") ыIуагъ, ятIонэрэм "унэгъо пытэ" (крепкая семья) ары.</t>
+        </is>
       </c>
       <c r="F213" s="3">
         <v>13</v>
@@ -13767,7 +13866,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T213" s="5"/>
+      <c r="T213" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="214" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
@@ -13782,8 +13885,10 @@
       <c r="D214" s="3">
         <v>6</v>
       </c>
-      <c r="E214" s="2" t="s">
-        <v>486</v>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Гущыӏэ шапхъэхэми заулэ зэфэшъхьаф — мыхэр мэхьанэшхо зимыIэ, зэдзэкIыным ынэкъокъугъэ шIыкIэхэр ары.</t>
+        </is>
       </c>
       <c r="F214" s="3">
         <v>11</v>
@@ -13811,7 +13916,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T214" s="5"/>
+      <c r="T214" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="215" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
@@ -13826,8 +13935,10 @@
       <c r="D215" s="3">
         <v>7</v>
       </c>
-      <c r="E215" s="2" t="s">
-        <v>487</v>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ау лъэпкъ мэхьанэ зиIэр — свадьбэ / день рождения зэфэшъхьафныгъэр ары.</t>
+        </is>
       </c>
       <c r="F215" s="3">
         <v>9</v>
@@ -13855,7 +13966,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T215" s="5"/>
+      <c r="T215" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
+      </c>
     </row>
     <row r="216" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
@@ -13927,13 +14042,11 @@
         <v>3</v>
       </c>
       <c r="I217" s="4"/>
-      <c r="J217" s="4">
-        <v>2</v>
-      </c>
+      <c r="J217" s="4"/>
       <c r="K217" s="4"/>
       <c r="L217" s="3">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M217" s="4"/>
       <c r="N217" s="4"/>
@@ -13945,8 +14058,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T217" s="5" t="s">
-        <v>563</v>
+      <c r="T217" s="5" t="inlineStr">
+        <is>
+          <t>Yazı sistemi karışıklığı.</t>
+        </is>
       </c>
     </row>
     <row r="218" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
@@ -14865,7 +14980,7 @@
       </c>
       <c r="C5" s="3">
         <f>SUMIFS(Sentences!$H:$H,Sentences!$C:$C,"1")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3">
         <f>SUMIFS(Sentences!$I:$I,Sentences!$C:$C,"1")</f>
@@ -14877,7 +14992,7 @@
       </c>
       <c r="F5" s="3">
         <f>SUMIFS(Sentences!$K:$K,Sentences!$C:$C,"1")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="3">
         <f>C5+D5+E5+F5</f>
@@ -14947,7 +15062,7 @@
       </c>
       <c r="E7" s="3">
         <f>SUMIFS(Sentences!$J:$J,Sentences!$C:$C,"3")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7" s="3">
         <f>SUMIFS(Sentences!$K:$K,Sentences!$C:$C,"3")</f>
@@ -14955,11 +15070,11 @@
       </c>
       <c r="G7" s="3">
         <f>C7+D7+E7+F7</f>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H7" s="3">
         <f>IF(B7=0,0,(C7+D7+E7+F7)*100/B7)</f>
-        <v>12.459016393442623</v>
+        <v>11.803278688524591</v>
       </c>
       <c r="I7" s="3">
         <f>SUMIFS(Sentences!$M:$M,Sentences!$C:$C,"3")</f>
@@ -14976,11 +15091,11 @@
       </c>
       <c r="C8" s="3">
         <f>SUMIFS(Sentences!$H:$H,Sentences!$C:$C,"4")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="3">
         <f>SUMIFS(Sentences!$I:$I,Sentences!$C:$C,"4")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3">
         <f>SUMIFS(Sentences!$J:$J,Sentences!$C:$C,"4")</f>
@@ -15013,11 +15128,11 @@
       </c>
       <c r="C9" s="3">
         <f>SUMIFS(Sentences!$H:$H,Sentences!$C:$C,"5")</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3">
         <f>SUMIFS(Sentences!$I:$I,Sentences!$C:$C,"5")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3">
         <f>SUMIFS(Sentences!$J:$J,Sentences!$C:$C,"5")</f>
@@ -15029,11 +15144,11 @@
       </c>
       <c r="G9" s="3">
         <f>C9+D9+E9+F9</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H9" s="3">
         <f>IF(B9=0,0,(C9+D9+E9+F9)*100/B9)</f>
-        <v>10.95890410958904</v>
+        <v>12.328767123287671</v>
       </c>
       <c r="I9" s="3">
         <f>SUMIFS(Sentences!$M:$M,Sentences!$C:$C,"5")</f>
@@ -15133,11 +15248,11 @@
       </c>
       <c r="B17" s="3">
         <f>COUNTIFS(Sentences!$C:$C,"5",Sentences!$G:$G,"doğru / правильно")</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3">
         <f>COUNTIFS(Sentences!$C:$C,"5",Sentences!$G:$G,"yanlış ama anlaşılır / понятно")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" s="3">
         <f>COUNTIFS(Sentences!$C:$C,"5",Sentences!$G:$G,"yanlış ve anlamsız / непонятно")</f>
@@ -15504,7 +15619,7 @@
       </c>
       <c r="B48" s="3">
         <f>SUMIFS(Sentences!$N:$N,Sentences!$C:$C,"1")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C48" s="3">
         <f>SUMIFS(Sentences!$O:$O,Sentences!$C:$C,"1")</f>
@@ -15524,7 +15639,7 @@
       </c>
       <c r="G48" s="3">
         <f>SUMIFS(Sentences!$S:$S,Sentences!$C:$C,"1")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
